--- a/Employee_Reports_wi48/Sivagaran Ramanathan Q0128.xlsx
+++ b/Employee_Reports_wi48/Sivagaran Ramanathan Q0128.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1461,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-347</v>
+        <v>-350</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-347</v>
+        <v>-350</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1596,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1645,11 +1645,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1694,11 +1694,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1731,11 +1731,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1768,11 +1768,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1805,11 +1805,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1854,11 +1854,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1891,11 +1891,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
